--- a/接口_P0_test_cases.xlsx
+++ b/接口_P0_test_cases.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.005" bestFit="1" customWidth="1" style="5" min="1" max="1"/>
@@ -1281,12 +1281,12 @@
     <row r="10" ht="33.75" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>P0-ORDER-003</t>
+          <t>P0-GOOD-001</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>订单支付流转</t>
+          <t>商品</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>已登录且存在可支付订单号</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
@@ -1306,15 +1306,15 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>/api/order/paid/{orderNo}</t>
+          <t>/api/good</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>token: {token}</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="n"/>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n"/>
       <c r="I10" s="1" t="n"/>
       <c r="J10" s="1" t="n"/>
       <c r="K10" s="1" t="n"/>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>SELECT status FROM orders WHERE order_no={{orderNo}};</t>
+          <t>SELECT COUNT(1) FROM good WHERE status=1;</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>not null</t>
+          <t>&gt;=0</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1346,99 +1346,610 @@
       <c r="Q10" s="1" t="n"/>
       <c r="R10" s="1" t="inlineStr">
         <is>
-          <t>调用订单支付接口</t>
+          <t>查询前台商品列表</t>
         </is>
       </c>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>smoke|order|payment</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>orderNo优先取配置orderNoPaid，&amp;#10;否则取提取变量</t>
+          <t>smoke|good</t>
+        </is>
+      </c>
+      <c r="T10" s="1" t="inlineStr">
+        <is>
+          <t>商品列表冒烟</t>
         </is>
       </c>
     </row>
     <row r="11" ht="23.25" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>P0-GOOD-001</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P0-CART-001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cart-add</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>已登录用户</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>/api/cart</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>res.json.code</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>从商品列表取一个goodId后执行加购</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>smoke,cart,add</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>根据抓包确认：POST /api/cart；代码保留多路径兼容探测作为兜底</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P0-PAY-001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>支付创建成功</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>已登录，存在可支付订单</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>/api/good</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="1" t="n"/>
-      <c r="J11" s="1" t="n"/>
-      <c r="K11" s="1" t="n"/>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>/api/order/paid/{orderNo}</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>token: {token}</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>res.json.code</t>
         </is>
       </c>
-      <c r="M11" s="1" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="N11" s="1" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(1) FROM good WHERE status=1;</t>
-        </is>
-      </c>
-      <c r="O11" s="1" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-      <c r="P11" s="1" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>SELECT state FROM t_order WHERE order_no={{orderNo}} LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>not null</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="Q11" s="1" t="n"/>
-      <c r="R11" s="1" t="inlineStr">
-        <is>
-          <t>查询前台商品列表</t>
-        </is>
-      </c>
-      <c r="S11" s="1" t="inlineStr">
-        <is>
-          <t>smoke|good</t>
-        </is>
-      </c>
-      <c r="T11" s="1" t="inlineStr">
-        <is>
-          <t>商品列表冒烟</t>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>选择可支付订单调用支付接口并校验成功</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>smoke|order|payment</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>正向流程</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P0-PAY-002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>支付缺参</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>已登录</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>/api/order/paid</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>token: {token}</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>res.status_code</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>400|404|405</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>缺失orderNo调用支付接口</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>smoke|order|payment|negative</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>应明确错误且不返回500</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P0-PAY-003</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>支付金额非法</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>已登录</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>/api/order/paid/{orderNo}</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>token: {token}</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>res.text</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>API_NO_AMOUNT_FIELD</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>尝试传递非法amount</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>smoke|order|payment|negative</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>当前接口无amount字段，需新支付创建接口支持</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P0-PAY-004</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>订单不存在</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>已登录</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>/api/order/paid/{orderNo}</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>token: {token}</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>res.json.code</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>!=200</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>传入不存在orderNo</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>smoke|order|payment|negative</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>应返回业务错误而非500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P0-PAY-005</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>重复支付幂等</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>已登录，存在已支付订单</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>/api/order/paid/{orderNo}</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>token: {token}</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>res.status_code</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>对已支付订单重复支付</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>smoke|order|payment|idempotency</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>应幂等或提示已支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P0-PAY-006</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>支付回调成功</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>已登录</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>/api/payment/callback</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>res.status_code</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>模拟支付成功回调</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>smoke|order|payment|callback</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>待补充回调契约URL/签名/字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P0-PAY-007</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>下游超时</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>已登录</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>/api/order/paid/{orderNo}</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>token: {token}</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>res.text</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>支付服务繁忙</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>模拟下游支付超时</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>smoke|order|payment|resilience</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>待补充mock框架与注入点</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P0-PAY-008</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>未授权支付</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>不带有效token</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>/api/order/paid/{orderNo}</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>res.json.code</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>401|403</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>无token调用支付接口</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>smoke|order|payment|security</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>应返回401/403</t>
         </is>
       </c>
     </row>
